--- a/df_GAM130326.xlsx
+++ b/df_GAM130326.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexi\Documents\Gaps SST sensitivity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexi\Downloads\Paleoclimatic-drivers-of-Acropora-palmata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D7A2EF-0413-4839-9A82-4C51D602F0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAE32F1-6E1A-49A2-94F3-53581E80A5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{14C25494-3685-40EA-A169-D3DD047310AF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{14C25494-3685-40EA-A169-D3DD047310AF}"/>
   </bookViews>
   <sheets>
     <sheet name="df_v1_GAM" sheetId="1" r:id="rId1"/>
@@ -430,7 +430,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -747,7 +747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D023390-1F3D-4850-8978-03A11C46D006}">
   <dimension ref="A1:J61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -881,13 +881,13 @@
         <v>13.188118811881187</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1046,7 +1046,7 @@
         <v>13.455445544554456</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>81</v>
@@ -1277,7 +1277,7 @@
         <v>15.089108910891088</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>11</v>
@@ -1310,7 +1310,7 @@
         <v>9.8217821782178216</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>11</v>
@@ -1343,7 +1343,7 @@
         <v>11.089108910891088</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>11</v>
@@ -1376,7 +1376,7 @@
         <v>9.6831683168316829</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>11</v>
@@ -1409,7 +1409,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -1442,7 +1442,7 @@
         <v>8.227722772277227</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>13</v>
@@ -2780,7 +2780,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD3A89E-F2B2-4C2A-BAA6-B56384D2CE53}">
   <dimension ref="A1:E171"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4">
